--- a/inquiry_forms/021_wireless_security_camera_subscription_free_purchase_inquiry--inquiry_forms.xlsx
+++ b/inquiry_forms/021_wireless_security_camera_subscription_free_purchase_inquiry--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -742,8 +742,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,12 +771,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'wireless_security_system',_'value':_'wireless_security_system'}</t>
+          <t>wireless_security_system</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Wireless Security System', 'value': 'wireless_security_system'}</t>
+          <t>Wireless Security System</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'security_camera',_'value':_'security_camera'}</t>
+          <t>security_camera</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Security Camera', 'value': 'security_camera'}</t>
+          <t>Security Camera</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'smart_doorbell',_'value':_'smart_doorbell'}</t>
+          <t>smart_doorbell</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Smart Doorbell', 'value': 'smart_doorbell'}</t>
+          <t>Smart Doorbell</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'video_security_system',_'value':_'video_security_system'}</t>
+          <t>video_security_system</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Video Security System', 'value': 'video_security_system'}</t>
+          <t>Video Security System</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'basic',_'value':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Basic', 'value': 'basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'advanced',_'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced', 'value': 'advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'premium',_'value':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Premium', 'value': 'premium'}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
